--- a/arabic_english_codeswitching_300.xlsx
+++ b/arabic_english_codeswitching_300.xlsx
@@ -2641,7 +2641,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>اشتريت gift card لصديقتي بمناسبة عيد ميلادها.</t>
+          <t>اشتريت gift card لصديقتي بمناسبة تخرجها.</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">

--- a/arabic_english_codeswitching_300.xlsx
+++ b/arabic_english_codeswitching_300.xlsx
@@ -829,7 +829,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>الـ pipeline توقف بسبب خطأ في الـ config! لازم نصلحه الحين.</t>
+          <t>الـ pipeline توقف بسبب خطأ في الـ config ! لازم نصلحه الحين.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>جرب تستخدم Postman عشان تختبر الـ API!</t>
+          <t>جرب تستخدم Postman عشان تختبر الـ API !</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2977,7 +2977,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>وصلت لمرحلة الـ checkout، بس ليش الموقع يتوقف كل مرة؟</t>
+          <t>وصلت لمرحلة الـ checkout ، بس ليش الموقع يتوقف كل مرة؟</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>أرسلت له رسالة على WhatsApp، ليش ما رد لين الحين؟</t>
+          <t>أرسلت له رسالة على WhatsApp ، ليش ما رد لين الحين؟</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">

--- a/arabic_english_codeswitching_300.xlsx
+++ b/arabic_english_codeswitching_300.xlsx
@@ -565,7 +565,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>عملنا merge للـ branch في Git بعد المراجعة.</t>
+          <t>سوينا merge للـ branch في Git بعد المراجعة.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>الـ query بطيء لازم نعمل له optimize.</t>
+          <t>الـ query بطيء لازم نسوي له optimize.</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>لازم نعمل test للـ feature قبل ما نطلعها.</t>
+          <t>لازم نسوي test للـ feature قبل ما نطلعها.</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>عملنا setup لبيئة العمل على الـ cloud.</t>
+          <t>سوينا setup لبيئة العمل على الـ cloud.</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>لازم نعمل refactor للكود عشان يصير أنظف.</t>
+          <t>لازم نسوي refactor للكود عشان يصير أنظف.</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>عملت repost للـ tweet اللي عجبني.</t>
+          <t>سويت repost للـ tweet اللي عجبني.</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>عملت block لحساب مزعج على X.</t>
+          <t>سويت block لحساب مزعج على X.</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>عملت share للمنشور في الـ group.</t>
+          <t>سويت share للمنشور في الـ group.</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>الحساب انعمله suspend بدون سبب واضح، للأسف!</t>
+          <t>صار على الحساب suspend بدون سبب واضح، للأسف!</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>عملت follow للحساب الجديد اللي فتحوه.</t>
+          <t>سويت follow للحساب الجديد اللي فتحوه.</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>المؤثر عمل review صادق عن المنتج.</t>
+          <t>المؤثر سوى review صادق عن المنتج.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>عملت subscribe لقناته الجديدة على YouTube.</t>
+          <t>سويت subscribe لقناته الجديدة على YouTube.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>عملنا collab مع حساب ثاني بنفس المجال.</t>
+          <t>سوينا collab مع حساب ثاني بنفس المجال.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>عملنا schedule لاجتماع الأسبوع الجاي.</t>
+          <t>سوينا schedule لاجتماع الأسبوع الجاي.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>عملت attach للملف قبل ما أرسل الإيميل.</t>
+          <t>سويت attach للملف قبل ما أرسل الإيميل.</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>عملت approve على الطلب المالي.</t>
+          <t>سويت approve على الطلب المالي.</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>لازم أعمل update للنظام قبل النوم.</t>
+          <t>لازم أسوي update للنظام قبل النوم.</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>عملت sync بين الجوال واللابتوب.</t>
+          <t>سويت sync بين الجوال واللابتوب.</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -2365,7 +2365,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>الجوال دايم يعمل lag وقت فتح التطبيقات.</t>
+          <t>الجوال دايم يسوي lag وقت فتح التطبيقات.</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>عملت subscription شهري لتطبيق التمارين.</t>
+          <t>سويت subscription شهري لتطبيق التمارين.</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>عملت check-in مبكر عن طريق التطبيق.</t>
+          <t>سويت check-in مبكر عن طريق التطبيق.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -3193,7 +3193,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>عملت refund للطلب لأنه تأخر كثير.</t>
+          <t>سويت refund للطلب لأنه تأخر كثير.</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>عملت compare بين سعر المتجر والمتجر المنافس.</t>
+          <t>سويت compare بين سعر المتجر والمتجر المنافس.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>عملت order من تطبيق Jarir للأدوات المكتبية.</t>
+          <t>سويت order من تطبيق Jarir للأدوات المكتبية.</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -3553,7 +3553,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>عملت install للتطبيق وواجهت مشكلة.</t>
+          <t>سويت install للتطبيق وواجهت مشكلة.</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>عملت update للتطبيق عشان أحل المشكلة.</t>
+          <t>سويت update للتطبيق عشان أحل المشكلة.</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>عملت mute لمجموعة الواتساب المزعجة.</t>
+          <t>سويت mute لمجموعة الواتساب المزعجة.</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>عملت forward للرسالة لصديقي.</t>
+          <t>سويت forward للرسالة لصديقي.</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>عملت clear للـ cache عشان يشتغل أسرع.</t>
+          <t>سويت clear للـ cache عشان يشتغل أسرع.</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -3841,7 +3841,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>الجوال صار يعمل freeze بسبب كثرة التطبيقات.</t>
+          <t>الجوال صار يسوي freeze بسبب كثرة التطبيقات.</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>عملت restart سريع للجوال بعد ما تعلق.</t>
+          <t>سويت restart سريع للجوال بعد ما تعلق.</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>عملت verify لرقمي بعد ما نزلت التطبيق.</t>
+          <t>سويت verify لرقمي بعد ما نزلت التطبيق.</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>عملت report لحساب مزيف يتصل بالناس.</t>
+          <t>سويت report لحساب مزيف يتصل بالناس.</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>عملت transfer للملفات بين الجوالين بسرعة.</t>
+          <t>سويت transfer للملفات بين الجوالين بسرعة.</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
